--- a/data/Aim 2.3 Sediment Sample Code.xlsx
+++ b/data/Aim 2.3 Sediment Sample Code.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/af327/Desktop/R/encapsulation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A3BDB5-E7F5-4345-A4F5-1334AACE409E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E669D9-C55A-154E-8ADC-6E59D373A43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27260" yWindow="-1460" windowWidth="27240" windowHeight="21100" xr2:uid="{EF7130B3-39CF-DD47-935B-E3A577CA84D9}"/>
+    <workbookView xWindow="-27260" yWindow="-860" windowWidth="27240" windowHeight="20500" xr2:uid="{EF7130B3-39CF-DD47-935B-E3A577CA84D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -194,150 +194,6 @@
     <t>REP-S-C-0</t>
   </si>
   <si>
-    <t>MC-E-A-21</t>
-  </si>
-  <si>
-    <t>MC-E-B-21</t>
-  </si>
-  <si>
-    <t>MC-E-C-21</t>
-  </si>
-  <si>
-    <t>MC-F-A-21</t>
-  </si>
-  <si>
-    <t>MC-F-B-21</t>
-  </si>
-  <si>
-    <t>MC-F-C-21</t>
-  </si>
-  <si>
-    <t>MC-N-A-21</t>
-  </si>
-  <si>
-    <t>MC-N-B-21</t>
-  </si>
-  <si>
-    <t>MC-N-C-21</t>
-  </si>
-  <si>
-    <t>MC-S-A-21</t>
-  </si>
-  <si>
-    <t>MC-S-B-21</t>
-  </si>
-  <si>
-    <t>MC-S-C-21</t>
-  </si>
-  <si>
-    <t>MCS-E-A-21</t>
-  </si>
-  <si>
-    <t>MCS-E-B-21</t>
-  </si>
-  <si>
-    <t>MCS-E-C-21</t>
-  </si>
-  <si>
-    <t>MCS-F-A-21</t>
-  </si>
-  <si>
-    <t>MCS-F-B-21</t>
-  </si>
-  <si>
-    <t>MCS-F-C-21</t>
-  </si>
-  <si>
-    <t>MCS-N-A-21</t>
-  </si>
-  <si>
-    <t>MCS-N-B-21</t>
-  </si>
-  <si>
-    <t>MCS-N-C-21</t>
-  </si>
-  <si>
-    <t>MCS-S-A-21</t>
-  </si>
-  <si>
-    <t>MCS-S-B-21</t>
-  </si>
-  <si>
-    <t>MCS-S-C-21</t>
-  </si>
-  <si>
-    <t>PC-E-A-21</t>
-  </si>
-  <si>
-    <t>PC-E-B-21</t>
-  </si>
-  <si>
-    <t>PC-E-C-21</t>
-  </si>
-  <si>
-    <t>PC-F-A-21</t>
-  </si>
-  <si>
-    <t>PC-F-B-21</t>
-  </si>
-  <si>
-    <t>PC-F-C-21</t>
-  </si>
-  <si>
-    <t>PC-N-A-21</t>
-  </si>
-  <si>
-    <t>PC-N-B-21</t>
-  </si>
-  <si>
-    <t>PC-N-C-21</t>
-  </si>
-  <si>
-    <t>PC-S-A-21</t>
-  </si>
-  <si>
-    <t>PC-S-B-21</t>
-  </si>
-  <si>
-    <t>PC-S-C-21</t>
-  </si>
-  <si>
-    <t>REP-E-A-21</t>
-  </si>
-  <si>
-    <t>REP-E-B-21</t>
-  </si>
-  <si>
-    <t>REP-E-C-21</t>
-  </si>
-  <si>
-    <t>REP-F-A-21</t>
-  </si>
-  <si>
-    <t>REP-F-B-21</t>
-  </si>
-  <si>
-    <t>REP-F-C-21</t>
-  </si>
-  <si>
-    <t>REP-N-A-21</t>
-  </si>
-  <si>
-    <t>REP-N-B-21</t>
-  </si>
-  <si>
-    <t>REP-N-C-21</t>
-  </si>
-  <si>
-    <t>REP-S-A-21</t>
-  </si>
-  <si>
-    <t>REP-S-B-21</t>
-  </si>
-  <si>
-    <t>REP-S-C-21</t>
-  </si>
-  <si>
     <t>MC-E-A-42</t>
   </si>
   <si>
@@ -480,6 +336,150 @@
   </si>
   <si>
     <t>REP-S-C-42</t>
+  </si>
+  <si>
+    <t>MC-E-A-14</t>
+  </si>
+  <si>
+    <t>MC-E-B-14</t>
+  </si>
+  <si>
+    <t>MC-E-C-14</t>
+  </si>
+  <si>
+    <t>MC-F-A-14</t>
+  </si>
+  <si>
+    <t>MC-F-B-14</t>
+  </si>
+  <si>
+    <t>MC-F-C-14</t>
+  </si>
+  <si>
+    <t>MC-N-A-14</t>
+  </si>
+  <si>
+    <t>MC-N-B-14</t>
+  </si>
+  <si>
+    <t>MC-N-C-14</t>
+  </si>
+  <si>
+    <t>MC-S-A-14</t>
+  </si>
+  <si>
+    <t>MC-S-B-14</t>
+  </si>
+  <si>
+    <t>MC-S-C-14</t>
+  </si>
+  <si>
+    <t>MCS-E-A-14</t>
+  </si>
+  <si>
+    <t>MCS-E-B-14</t>
+  </si>
+  <si>
+    <t>MCS-E-C-14</t>
+  </si>
+  <si>
+    <t>MCS-F-A-14</t>
+  </si>
+  <si>
+    <t>MCS-F-B-14</t>
+  </si>
+  <si>
+    <t>MCS-F-C-14</t>
+  </si>
+  <si>
+    <t>MCS-N-A-14</t>
+  </si>
+  <si>
+    <t>MCS-N-B-14</t>
+  </si>
+  <si>
+    <t>MCS-N-C-14</t>
+  </si>
+  <si>
+    <t>MCS-S-A-14</t>
+  </si>
+  <si>
+    <t>MCS-S-B-14</t>
+  </si>
+  <si>
+    <t>MCS-S-C-14</t>
+  </si>
+  <si>
+    <t>PC-E-A-14</t>
+  </si>
+  <si>
+    <t>PC-E-B-14</t>
+  </si>
+  <si>
+    <t>PC-E-C-14</t>
+  </si>
+  <si>
+    <t>PC-F-A-14</t>
+  </si>
+  <si>
+    <t>PC-F-B-14</t>
+  </si>
+  <si>
+    <t>PC-F-C-14</t>
+  </si>
+  <si>
+    <t>PC-N-A-14</t>
+  </si>
+  <si>
+    <t>PC-N-B-14</t>
+  </si>
+  <si>
+    <t>PC-N-C-14</t>
+  </si>
+  <si>
+    <t>PC-S-A-14</t>
+  </si>
+  <si>
+    <t>PC-S-B-14</t>
+  </si>
+  <si>
+    <t>PC-S-C-14</t>
+  </si>
+  <si>
+    <t>REP-E-A-14</t>
+  </si>
+  <si>
+    <t>REP-E-B-14</t>
+  </si>
+  <si>
+    <t>REP-E-C-14</t>
+  </si>
+  <si>
+    <t>REP-F-A-14</t>
+  </si>
+  <si>
+    <t>REP-F-B-14</t>
+  </si>
+  <si>
+    <t>REP-F-C-14</t>
+  </si>
+  <si>
+    <t>REP-N-A-14</t>
+  </si>
+  <si>
+    <t>REP-N-B-14</t>
+  </si>
+  <si>
+    <t>REP-N-C-14</t>
+  </si>
+  <si>
+    <t>REP-S-A-14</t>
+  </si>
+  <si>
+    <t>REP-S-B-14</t>
+  </si>
+  <si>
+    <t>REP-S-C-14</t>
   </si>
 </sst>
 </file>
@@ -1839,11 +1839,11 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="B74" s="4" t="str">
         <f>REPLACE(A74, 1, 2, "M")</f>
-        <v>M-E-A-21</v>
+        <v>M-E-A-14</v>
       </c>
       <c r="C74">
         <v>58</v>
@@ -1851,11 +1851,11 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="B75" s="4" t="str">
         <f t="shared" ref="B75:B91" si="4">REPLACE(A75, 1, 2, "M")</f>
-        <v>M-E-B-21</v>
+        <v>M-E-B-14</v>
       </c>
       <c r="C75">
         <v>59</v>
@@ -1863,11 +1863,11 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="B76" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-E-C-21</v>
+        <v>M-E-C-14</v>
       </c>
       <c r="C76">
         <v>60</v>
@@ -1876,11 +1876,11 @@
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="str">
         <f>A74 &amp; "-D"</f>
-        <v>MC-E-A-21-D</v>
+        <v>MC-E-A-14-D</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-E-A-21-D</v>
+        <v>M-E-A-14-D</v>
       </c>
       <c r="C77">
         <v>172</v>
@@ -1889,11 +1889,11 @@
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="str">
         <f>A75 &amp; "-D"</f>
-        <v>MC-E-B-21-D</v>
+        <v>MC-E-B-14-D</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-E-B-21-D</v>
+        <v>M-E-B-14-D</v>
       </c>
       <c r="C78">
         <v>173</v>
@@ -1902,11 +1902,11 @@
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="str">
         <f>A76 &amp; "-D"</f>
-        <v>MC-E-C-21-D</v>
+        <v>MC-E-C-14-D</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-E-C-21-D</v>
+        <v>M-E-C-14-D</v>
       </c>
       <c r="C79">
         <v>174</v>
@@ -1914,11 +1914,11 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-F-A-21</v>
+        <v>M-F-A-14</v>
       </c>
       <c r="C80">
         <v>49</v>
@@ -1926,11 +1926,11 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-F-B-21</v>
+        <v>M-F-B-14</v>
       </c>
       <c r="C81">
         <v>50</v>
@@ -1938,11 +1938,11 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-F-C-21</v>
+        <v>M-F-C-14</v>
       </c>
       <c r="C82">
         <v>51</v>
@@ -1950,11 +1950,11 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-N-A-21</v>
+        <v>M-N-A-14</v>
       </c>
       <c r="C83">
         <v>52</v>
@@ -1962,11 +1962,11 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-N-B-21</v>
+        <v>M-N-B-14</v>
       </c>
       <c r="C84">
         <v>53</v>
@@ -1974,11 +1974,11 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>M-N-C-21</v>
+        <v>M-N-C-14</v>
       </c>
       <c r="C85">
         <v>54</v>
@@ -1986,11 +1986,11 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B86" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M-S-A-21</v>
+        <v>M-S-A-14</v>
       </c>
       <c r="C86">
         <v>55</v>
@@ -1998,11 +1998,11 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B87" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M-S-B-21</v>
+        <v>M-S-B-14</v>
       </c>
       <c r="C87">
         <v>56</v>
@@ -2010,11 +2010,11 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="9" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="B88" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M-S-C-21</v>
+        <v>M-S-C-14</v>
       </c>
       <c r="C88">
         <v>57</v>
@@ -2023,11 +2023,11 @@
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="str">
         <f>A86 &amp; "-D"</f>
-        <v>MC-S-A-21-D</v>
+        <v>MC-S-A-14-D</v>
       </c>
       <c r="B89" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M-S-A-21-D</v>
+        <v>M-S-A-14-D</v>
       </c>
       <c r="C89">
         <v>169</v>
@@ -2036,11 +2036,11 @@
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="str">
         <f>A87 &amp; "-D"</f>
-        <v>MC-S-B-21-D</v>
+        <v>MC-S-B-14-D</v>
       </c>
       <c r="B90" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M-S-B-21-D</v>
+        <v>M-S-B-14-D</v>
       </c>
       <c r="C90">
         <v>170</v>
@@ -2049,11 +2049,11 @@
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="str">
         <f>A88 &amp; "-D"</f>
-        <v>MC-S-C-21-D</v>
+        <v>MC-S-C-14-D</v>
       </c>
       <c r="B91" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>M-S-C-21-D</v>
+        <v>M-S-C-14-D</v>
       </c>
       <c r="C91">
         <v>171</v>
@@ -2061,11 +2061,11 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B92" s="1" t="str">
         <f>REPLACE(A92, 1, 3, "S")</f>
-        <v>S-E-A-21</v>
+        <v>S-E-A-14</v>
       </c>
       <c r="C92">
         <v>70</v>
@@ -2073,11 +2073,11 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B93" s="1" t="str">
         <f t="shared" ref="B93:B109" si="5">REPLACE(A93, 1, 3, "S")</f>
-        <v>S-E-B-21</v>
+        <v>S-E-B-14</v>
       </c>
       <c r="C93">
         <v>71</v>
@@ -2085,11 +2085,11 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B94" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>S-E-C-21</v>
+        <v>S-E-C-14</v>
       </c>
       <c r="C94">
         <v>72</v>
@@ -2098,11 +2098,11 @@
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="str">
         <f>A92 &amp; "-D"</f>
-        <v>MCS-E-A-21-D</v>
+        <v>MCS-E-A-14-D</v>
       </c>
       <c r="B95" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>S-E-A-21-D</v>
+        <v>S-E-A-14-D</v>
       </c>
       <c r="C95">
         <v>178</v>
@@ -2111,11 +2111,11 @@
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="str">
         <f>A93 &amp; "-D"</f>
-        <v>MCS-E-B-21-D</v>
+        <v>MCS-E-B-14-D</v>
       </c>
       <c r="B96" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>S-E-B-21-D</v>
+        <v>S-E-B-14-D</v>
       </c>
       <c r="C96">
         <v>179</v>
@@ -2124,11 +2124,11 @@
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="str">
         <f>A94 &amp; "-D"</f>
-        <v>MCS-E-C-21-D</v>
+        <v>MCS-E-C-14-D</v>
       </c>
       <c r="B97" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>S-E-C-21-D</v>
+        <v>S-E-C-14-D</v>
       </c>
       <c r="C97">
         <v>180</v>
@@ -2136,11 +2136,11 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-F-A-21</v>
+        <v>S-F-A-14</v>
       </c>
       <c r="C98">
         <v>61</v>
@@ -2148,11 +2148,11 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-F-B-21</v>
+        <v>S-F-B-14</v>
       </c>
       <c r="C99">
         <v>62</v>
@@ -2160,11 +2160,11 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-F-C-21</v>
+        <v>S-F-C-14</v>
       </c>
       <c r="C100">
         <v>63</v>
@@ -2172,11 +2172,11 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-N-A-21</v>
+        <v>S-N-A-14</v>
       </c>
       <c r="C101">
         <v>64</v>
@@ -2184,11 +2184,11 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-N-B-21</v>
+        <v>S-N-B-14</v>
       </c>
       <c r="C102">
         <v>65</v>
@@ -2196,11 +2196,11 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-N-C-21</v>
+        <v>S-N-C-14</v>
       </c>
       <c r="C103">
         <v>66</v>
@@ -2208,11 +2208,11 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-S-A-21</v>
+        <v>S-S-A-14</v>
       </c>
       <c r="C104">
         <v>67</v>
@@ -2220,11 +2220,11 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-S-B-21</v>
+        <v>S-S-B-14</v>
       </c>
       <c r="C105">
         <v>68</v>
@@ -2232,11 +2232,11 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="9" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-S-C-21</v>
+        <v>S-S-C-14</v>
       </c>
       <c r="C106">
         <v>69</v>
@@ -2245,11 +2245,11 @@
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="str">
         <f>A104 &amp; "-D"</f>
-        <v>MCS-S-A-21-D</v>
+        <v>MCS-S-A-14-D</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-S-A-21-D</v>
+        <v>S-S-A-14-D</v>
       </c>
       <c r="C107">
         <v>175</v>
@@ -2258,11 +2258,11 @@
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="str">
         <f>A105 &amp; "-D"</f>
-        <v>MCS-S-B-21-D</v>
+        <v>MCS-S-B-14-D</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-S-B-21-D</v>
+        <v>S-S-B-14-D</v>
       </c>
       <c r="C108">
         <v>176</v>
@@ -2271,11 +2271,11 @@
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="str">
         <f>A106 &amp; "-D"</f>
-        <v>MCS-S-C-21-D</v>
+        <v>MCS-S-C-14-D</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>S-S-C-21-D</v>
+        <v>S-S-C-14-D</v>
       </c>
       <c r="C109">
         <v>177</v>
@@ -2283,11 +2283,11 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B110" s="1" t="str">
         <f>REPLACE(A110, 1, 2, "P")</f>
-        <v>P-E-A-21</v>
+        <v>P-E-A-14</v>
       </c>
       <c r="C110">
         <v>82</v>
@@ -2295,11 +2295,11 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="B111" s="1" t="str">
         <f t="shared" ref="B111:B127" si="6">REPLACE(A111, 1, 2, "P")</f>
-        <v>P-E-B-21</v>
+        <v>P-E-B-14</v>
       </c>
       <c r="C111">
         <v>83</v>
@@ -2307,11 +2307,11 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="B112" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-E-C-21</v>
+        <v>P-E-C-14</v>
       </c>
       <c r="C112">
         <v>84</v>
@@ -2320,11 +2320,11 @@
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="str">
         <f>A110 &amp; "-D"</f>
-        <v>PC-E-A-21-D</v>
+        <v>PC-E-A-14-D</v>
       </c>
       <c r="B113" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-E-A-21-D</v>
+        <v>P-E-A-14-D</v>
       </c>
       <c r="C113">
         <v>184</v>
@@ -2333,11 +2333,11 @@
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="str">
         <f>A111 &amp; "-D"</f>
-        <v>PC-E-B-21-D</v>
+        <v>PC-E-B-14-D</v>
       </c>
       <c r="B114" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-E-B-21-D</v>
+        <v>P-E-B-14-D</v>
       </c>
       <c r="C114">
         <v>185</v>
@@ -2346,11 +2346,11 @@
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="str">
         <f>A112 &amp; "-D"</f>
-        <v>PC-E-C-21-D</v>
+        <v>PC-E-C-14-D</v>
       </c>
       <c r="B115" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-E-C-21-D</v>
+        <v>P-E-C-14-D</v>
       </c>
       <c r="C115">
         <v>186</v>
@@ -2358,11 +2358,11 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="B116" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-F-A-21</v>
+        <v>P-F-A-14</v>
       </c>
       <c r="C116">
         <v>73</v>
@@ -2370,11 +2370,11 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="B117" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-F-B-21</v>
+        <v>P-F-B-14</v>
       </c>
       <c r="C117">
         <v>74</v>
@@ -2382,11 +2382,11 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B118" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-F-C-21</v>
+        <v>P-F-C-14</v>
       </c>
       <c r="C118">
         <v>75</v>
@@ -2394,11 +2394,11 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="B119" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-N-A-21</v>
+        <v>P-N-A-14</v>
       </c>
       <c r="C119">
         <v>76</v>
@@ -2406,11 +2406,11 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="B120" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-N-B-21</v>
+        <v>P-N-B-14</v>
       </c>
       <c r="C120">
         <v>77</v>
@@ -2418,11 +2418,11 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="B121" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>P-N-C-21</v>
+        <v>P-N-C-14</v>
       </c>
       <c r="C121">
         <v>78</v>
@@ -2430,11 +2430,11 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>P-S-A-21</v>
+        <v>P-S-A-14</v>
       </c>
       <c r="C122">
         <v>79</v>
@@ -2442,11 +2442,11 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>P-S-B-21</v>
+        <v>P-S-B-14</v>
       </c>
       <c r="C123">
         <v>80</v>
@@ -2454,11 +2454,11 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="9" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>P-S-C-21</v>
+        <v>P-S-C-14</v>
       </c>
       <c r="C124">
         <v>81</v>
@@ -2467,11 +2467,11 @@
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="str">
         <f>A122 &amp; "-D"</f>
-        <v>PC-S-A-21-D</v>
+        <v>PC-S-A-14-D</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>P-S-A-21-D</v>
+        <v>P-S-A-14-D</v>
       </c>
       <c r="C125">
         <v>181</v>
@@ -2480,11 +2480,11 @@
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="str">
         <f>A123 &amp; "-D"</f>
-        <v>PC-S-B-21-D</v>
+        <v>PC-S-B-14-D</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>P-S-B-21-D</v>
+        <v>P-S-B-14-D</v>
       </c>
       <c r="C126">
         <v>182</v>
@@ -2493,11 +2493,11 @@
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="str">
         <f>A124 &amp; "-D"</f>
-        <v>PC-S-C-21-D</v>
+        <v>PC-S-C-14-D</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="6"/>
-        <v>P-S-C-21-D</v>
+        <v>P-S-C-14-D</v>
       </c>
       <c r="C127">
         <v>183</v>
@@ -2505,11 +2505,11 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="B128" s="4" t="str">
         <f>REPLACE(A128, 1, 3, "R")</f>
-        <v>R-E-A-21</v>
+        <v>R-E-A-14</v>
       </c>
       <c r="C128">
         <v>94</v>
@@ -2517,11 +2517,11 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" ref="B129:B145" si="7">REPLACE(A129, 1, 3, "R")</f>
-        <v>R-E-B-21</v>
+        <v>R-E-B-14</v>
       </c>
       <c r="C129">
         <v>95</v>
@@ -2529,11 +2529,11 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>R-E-C-21</v>
+        <v>R-E-C-14</v>
       </c>
       <c r="C130">
         <v>96</v>
@@ -2542,11 +2542,11 @@
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="str">
         <f>A128 &amp; "-D"</f>
-        <v>REP-E-A-21-D</v>
+        <v>REP-E-A-14-D</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>R-E-A-21-D</v>
+        <v>R-E-A-14-D</v>
       </c>
       <c r="C131">
         <v>190</v>
@@ -2555,11 +2555,11 @@
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="str">
         <f>A129 &amp; "-D"</f>
-        <v>REP-E-B-21-D</v>
+        <v>REP-E-B-14-D</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>R-E-B-21-D</v>
+        <v>R-E-B-14-D</v>
       </c>
       <c r="C132">
         <v>191</v>
@@ -2568,11 +2568,11 @@
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="str">
         <f>A130 &amp; "-D"</f>
-        <v>REP-E-C-21-D</v>
+        <v>REP-E-C-14-D</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>R-E-C-21-D</v>
+        <v>R-E-C-14-D</v>
       </c>
       <c r="C133">
         <v>192</v>
@@ -2580,11 +2580,11 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="B134" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-F-A-21</v>
+        <v>R-F-A-14</v>
       </c>
       <c r="C134">
         <v>85</v>
@@ -2592,11 +2592,11 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="B135" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-F-B-21</v>
+        <v>R-F-B-14</v>
       </c>
       <c r="C135">
         <v>86</v>
@@ -2604,11 +2604,11 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="B136" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-F-C-21</v>
+        <v>R-F-C-14</v>
       </c>
       <c r="C136">
         <v>87</v>
@@ -2616,11 +2616,11 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="B137" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-N-A-21</v>
+        <v>R-N-A-14</v>
       </c>
       <c r="C137">
         <v>88</v>
@@ -2628,11 +2628,11 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="B138" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-N-B-21</v>
+        <v>R-N-B-14</v>
       </c>
       <c r="C138">
         <v>89</v>
@@ -2640,11 +2640,11 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="B139" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-N-C-21</v>
+        <v>R-N-C-14</v>
       </c>
       <c r="C139">
         <v>90</v>
@@ -2652,11 +2652,11 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="B140" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-S-A-21</v>
+        <v>R-S-A-14</v>
       </c>
       <c r="C140">
         <v>91</v>
@@ -2664,11 +2664,11 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="B141" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-S-B-21</v>
+        <v>R-S-B-14</v>
       </c>
       <c r="C141">
         <v>92</v>
@@ -2676,11 +2676,11 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="9" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="B142" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-S-C-21</v>
+        <v>R-S-C-14</v>
       </c>
       <c r="C142">
         <v>93</v>
@@ -2689,11 +2689,11 @@
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="str">
         <f>A140 &amp; "-D"</f>
-        <v>REP-S-A-21-D</v>
+        <v>REP-S-A-14-D</v>
       </c>
       <c r="B143" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-S-A-21-D</v>
+        <v>R-S-A-14-D</v>
       </c>
       <c r="C143">
         <v>187</v>
@@ -2702,11 +2702,11 @@
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="str">
         <f>A141 &amp; "-D"</f>
-        <v>REP-S-B-21-D</v>
+        <v>REP-S-B-14-D</v>
       </c>
       <c r="B144" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-S-B-21-D</v>
+        <v>R-S-B-14-D</v>
       </c>
       <c r="C144">
         <v>188</v>
@@ -2715,11 +2715,11 @@
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="str">
         <f>A142 &amp; "-D"</f>
-        <v>REP-S-C-21-D</v>
+        <v>REP-S-C-14-D</v>
       </c>
       <c r="B145" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>R-S-C-21-D</v>
+        <v>R-S-C-14-D</v>
       </c>
       <c r="C145">
         <v>189</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="B146" s="4" t="str">
         <f>REPLACE(A146, 1, 2, "M")</f>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" ref="B147:B163" si="8">REPLACE(A147, 1, 2, "M")</f>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="6" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="8"/>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B158" s="1" t="str">
         <f t="shared" si="8"/>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B159" s="1" t="str">
         <f t="shared" si="8"/>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="9" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="B160" s="1" t="str">
         <f t="shared" si="8"/>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="B164" s="1" t="str">
         <f>REPLACE(A164, 1, 3, "S")</f>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="B165" s="1" t="str">
         <f t="shared" ref="B165:B181" si="9">REPLACE(A165, 1, 3, "S")</f>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="6" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="B166" s="1" t="str">
         <f t="shared" si="9"/>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3036,7 +3036,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="9" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="9"/>
@@ -3171,7 +3171,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="B182" s="1" t="str">
         <f>REPLACE(A182, 1, 2, "P")</f>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="B183" s="1" t="str">
         <f t="shared" ref="B183:B198" si="10">REPLACE(A183, 1, 2, "P")</f>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="6" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="B184" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="B188" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="B189" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="B190" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="B191" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="B192" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="B193" s="1" t="str">
         <f t="shared" si="10"/>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="10"/>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="10"/>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="9" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="10"/>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B200" s="4" t="str">
         <f>REPLACE(A200, 1, 3, "R")</f>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" ref="B201:B217" si="11">REPLACE(A201, 1, 3, "R")</f>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="11"/>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="B206" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="B207" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="B208" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="B209" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="B210" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="B211" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="B212" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3543,7 +3543,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="8" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="B213" s="1" t="str">
         <f t="shared" si="11"/>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="9" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="B214" s="1" t="str">
         <f t="shared" si="11"/>
